--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574472909</v>
+        <v>46157.93117970689</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117970689</v>
+        <v>46157.93183631395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183631395</v>
+        <v>46157.93405756206</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405756206</v>
+        <v>46157.93723851709</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723851709</v>
+        <v>46158.28221634133</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221634133</v>
+        <v>46158.29702271441</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702271441</v>
+        <v>46158.29821382561</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821382561</v>
+        <v>46158.33392652206</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392652206</v>
+        <v>46158.36862440882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Грачев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862440882</v>
+        <v>46158.37293397979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
